--- a/Nexora-BI_VM_Resource_Requirement.xlsx
+++ b/Nexora-BI_VM_Resource_Requirement.xlsx
@@ -2589,7 +2589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" style="39" min="1" max="1"/>
@@ -2816,55 +2816,77 @@
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="40">
-      <c r="A13" s="43" t="n"/>
-      <c r="B13" s="43" t="n"/>
-      <c r="C13" s="43" t="n"/>
-      <c r="D13" s="43" t="n"/>
+      <c r="A13" s="60" t="inlineStr">
+        <is>
+          <t>D-09</t>
+        </is>
+      </c>
+      <c r="B13" s="62" t="inlineStr">
+        <is>
+          <t>Inbound write path from the CAD zone to the BI database tier: the CAD supplier (DS) will write a mirror of the CAD data views into a dedicated database (cad_mirror) on the BI PostgreSQL cluster, via pgBouncer over TLS. Source address range, firewall rule and approval are required.</t>
+        </is>
+      </c>
+      <c r="C13" s="62" t="inlineStr">
+        <is>
+          <t>Without this path the CAD incremental feed (IF-02) cannot operate. The database tier sizing is unaffected (tens of thousands of rows per day); only the network boundary changes. Until approved, development proceeds on data dumps supplied by DS.</t>
+        </is>
+      </c>
+      <c r="D13" s="62" t="inlineStr">
+        <is>
+          <t>Main Contractor / MOI network security</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="40">
-      <c r="A14" s="77" t="inlineStr">
-        <is>
-          <t>Scope boundary</t>
-        </is>
-      </c>
+      <c r="A14" s="43" t="n"/>
       <c r="B14" s="43" t="n"/>
       <c r="C14" s="43" t="n"/>
       <c r="D14" s="43" t="n"/>
     </row>
     <row r="15" ht="48" customHeight="1" s="40">
-      <c r="A15" s="58" t="inlineStr">
+      <c r="A15" s="77" t="inlineStr">
+        <is>
+          <t>Scope boundary</t>
+        </is>
+      </c>
+      <c r="B15" s="43" t="n"/>
+      <c r="C15" s="43" t="n"/>
+      <c r="D15" s="43" t="n"/>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="40">
+      <c r="A16" s="58" t="inlineStr">
         <is>
           <t>Three boundaries apply to this specification. First, the DMZ zone is provided and operated by the Main Contractor, including the WAF, DDoS protection, public DNS, TLS certificates and the SMS and e-mail gateways; this subsystem places only the two access proxies in that zone and requires them to be provisioned there. Second, mobile application management — MDM, application distribution and device compliance — is carried by the existing MOI platform and is outside the scope of this subsystem. Third, the DMZ hosts store no business data and no credential store: credentials are verified by the internal IAM service and the proxies forward requests only.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="40"/>
     <row r="17" ht="15" customHeight="1" s="40"/>
-    <row r="18" ht="15" customHeight="1" s="40">
-      <c r="A18" s="43" t="n"/>
-      <c r="B18" s="43" t="n"/>
-      <c r="C18" s="43" t="n"/>
-      <c r="D18" s="43" t="n"/>
-    </row>
+    <row r="18" ht="15" customHeight="1" s="40"/>
     <row r="19" ht="15" customHeight="1" s="40">
-      <c r="A19" s="77" t="inlineStr">
-        <is>
-          <t>Note on service-level dependency</t>
-        </is>
-      </c>
+      <c r="A19" s="43" t="n"/>
       <c r="B19" s="43" t="n"/>
       <c r="C19" s="43" t="n"/>
       <c r="D19" s="43" t="n"/>
     </row>
     <row r="20" ht="39.75" customHeight="1" s="40">
-      <c r="A20" s="58" t="inlineStr">
+      <c r="A20" s="77" t="inlineStr">
+        <is>
+          <t>Note on service-level dependency</t>
+        </is>
+      </c>
+      <c r="B20" s="43" t="n"/>
+      <c r="C20" s="43" t="n"/>
+      <c r="D20" s="43" t="n"/>
+    </row>
+    <row r="21" ht="15" customHeight="1" s="40">
+      <c r="A21" s="58" t="inlineStr">
         <is>
           <t>The availability and performance commitments made for the business intelligence, reporting and dashboard components assume that the infrastructure is provisioned, operated and maintained in accordance with this specification. Deviations should be agreed in writing so that the corresponding service-level expectations can be adjusted at the same time.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="40"/>
     <row r="22" ht="15" customHeight="1" s="40"/>
+    <row r="23"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
